--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T10:55:45+00:00</t>
+    <t>2023-04-05T15:18:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -338,11 +338,30 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>Extension.value[x]:valuePeriod</t>
+  </si>
+  <si>
+    <t>valuePeriod</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valuePeriod.id</t>
+  </si>
+  <si>
     <t>Extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valuePeriod.extension</t>
   </si>
   <si>
     <t>Extension.value[x].extension</t>
@@ -361,6 +380,9 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>Extension.value[x]:valuePeriod.start</t>
+  </si>
+  <si>
     <t>Extension.value[x].start</t>
   </si>
   <si>
@@ -388,6 +410,9 @@
   </si>
   <si>
     <t>./low</t>
+  </si>
+  <si>
+    <t>Extension.value[x]:valuePeriod.end</t>
   </si>
   <si>
     <t>Extension.value[x].end</t>
@@ -710,10 +735,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK10"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.109375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="27.703125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
@@ -1351,16 +1376,14 @@
         <v>74</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="AC6" s="2"/>
       <c r="AD6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>101</v>
@@ -1375,7 +1398,7 @@
         <v>79</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>100</v>
@@ -1383,12 +1406,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>109</v>
+      </c>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
@@ -1409,13 +1434,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1466,7 +1491,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -1475,32 +1500,32 @@
         <v>81</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1512,17 +1537,15 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>74</v>
@@ -1559,34 +1582,34 @@
         <v>74</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -1594,18 +1617,18 @@
         <v>112</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>74</v>
@@ -1614,10 +1637,10 @@
         <v>74</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>115</v>
@@ -1664,42 +1687,42 @@
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1719,10 +1742,10 @@
         <v>74</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>122</v>
@@ -1737,53 +1760,51 @@
       <c r="P10" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q10" t="s" s="2">
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF10" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="R10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -1792,13 +1813,120 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>127</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q11" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="R11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:18:36+00:00</t>
+    <t>2023-04-05T15:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:41:27+00:00</t>
+    <t>2023-04-05T15:52:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:52:08+00:00</t>
+    <t>2023-04-05T15:53:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:53:16+00:00</t>
+    <t>2023-04-05T15:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:55:13+00:00</t>
+    <t>2023-04-05T16:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:00:25+00:00</t>
+    <t>2023-04-05T16:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:20:25+00:00</t>
+    <t>2023-04-05T16:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:21:30+00:00</t>
+    <t>2023-04-05T16:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:24:37+00:00</t>
+    <t>2023-04-05T17:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T17:39:15+00:00</t>
+    <t>2023-04-07T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-07T12:42:40+00:00</t>
+    <t>2023-04-12T10:00:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:00:48+00:00</t>
+    <t>2023-04-12T10:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:05:52+00:00</t>
+    <t>2023-04-12T10:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:08:35+00:00</t>
+    <t>2023-04-12T14:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T14:03:54+00:00</t>
+    <t>2023-04-13T07:49:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T07:49:09+00:00</t>
+    <t>2023-04-13T08:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:12:13+00:00</t>
+    <t>2023-04-13T08:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:22:34+00:00</t>
+    <t>2023-04-13T08:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:33:21+00:00</t>
+    <t>2023-04-13T08:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:34:34+00:00</t>
+    <t>2023-04-13T08:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:54:00+00:00</t>
+    <t>2023-04-13T09:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T09:51:53+00:00</t>
+    <t>2023-04-13T10:21:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T10:21:56+00:00</t>
+    <t>2023-04-13T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T12:58:26+00:00</t>
+    <t>2023-04-13T15:00:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:00:08+00:00</t>
+    <t>2023-04-13T15:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:16:05+00:00</t>
+    <t>2023-04-14T12:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:31:23+00:00</t>
+    <t>2023-04-14T12:45:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:45:28+00:00</t>
+    <t>2023-04-14T13:02:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:02:26+00:00</t>
+    <t>2023-04-14T13:12:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:12:31+00:00</t>
+    <t>2023-04-17T08:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:15:24+00:00</t>
+    <t>2023-04-17T08:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:17:23+00:00</t>
+    <t>2023-04-17T08:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:37:32+00:00</t>
+    <t>2023-04-17T09:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T09:07:20+00:00</t>
+    <t>2023-04-17T10:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:39:40+00:00</t>
+    <t>2023-04-17T10:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:56:20+00:00</t>
+    <t>2023-04-17T11:14:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:14:19+00:00</t>
+    <t>2023-04-17T11:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:17:21+00:00</t>
+    <t>2023-04-17T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:39:02+00:00</t>
+    <t>2023-04-17T11:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:54:58+00:00</t>
+    <t>2023-04-17T12:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:02:32+00:00</t>
+    <t>2023-04-17T13:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T13:37:35+00:00</t>
+    <t>2023-04-17T14:05:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T14:05:09+00:00</t>
+    <t>2023-04-20T17:39:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:39:34+00:00</t>
+    <t>2023-04-20T17:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:42:03+00:00</t>
+    <t>2023-04-20T17:43:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:10+00:00</t>
+    <t>2023-04-20T17:43:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:52+00:00</t>
+    <t>2023-04-28T11:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:09:12+00:00</t>
+    <t>2023-04-28T15:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T15:03:41+00:00</t>
+    <t>2023-04-28T18:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:35:22+00:00</t>
+    <t>2023-04-28T18:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:37:07+00:00</t>
+    <t>2023-04-28T18:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:58:16+00:00</t>
+    <t>2023-05-02T06:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -393,13 +393,13 @@
 </t>
   </si>
   <si>
+    <t>datePremiereMEO</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.</t>
+  </si>
+  <si>
     <t>Date de mise en œuvre</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
   </si>
   <si>
     <t>Period.start</t>
@@ -418,13 +418,13 @@
     <t>Extension.value[x].end</t>
   </si>
   <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
+  </si>
+  <si>
     <t>Date de fin de mise en œuvre</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
   </si>
   <si>
     <t>If the end of the period is missing, it means that the period is ongoing</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:31:09+00:00</t>
+    <t>2023-05-02T06:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:34:44+00:00</t>
+    <t>2023-05-02T07:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T07:22:02+00:00</t>
+    <t>2023-05-02T14:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:04:27+00:00</t>
+    <t>2023-05-02T14:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:10:11+00:00</t>
+    <t>2023-05-02T14:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:20:51+00:00</t>
+    <t>2023-05-02T14:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:32:14+00:00</t>
+    <t>2023-05-02T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T15:50:41+00:00</t>
+    <t>2023-05-02T16:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T16:15:55+00:00</t>
+    <t>2023-05-02T17:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:25:18+00:00</t>
+    <t>2023-05-02T17:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:45:11+00:00</t>
+    <t>2023-05-02T17:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:46:32+00:00</t>
+    <t>2023-05-04T14:01:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:01:59+00:00</t>
+    <t>2023-05-04T14:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:04:48+00:00</t>
+    <t>2023-05-04T14:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-ext-device-Period-implantation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:08:50+00:00</t>
+    <t>2023-05-05T17:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -396,10 +396,10 @@
     <t>datePremiereMEO</t>
   </si>
   <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>Date de mise en œuvre</t>
+    <t>Date de première mise en œuvre de l'activité de soin.</t>
+  </si>
+  <si>
+    <t>Synonyme FINESS : date de mise en œuvre</t>
   </si>
   <si>
     <t>Period.start</t>
@@ -421,10 +421,10 @@
     <t>dateFin</t>
   </si>
   <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>Date de fin de mise en œuvre</t>
+    <t>Date d'échéance de l'autorisation.</t>
+  </si>
+  <si>
+    <t>Synonyme FINESS : date de fin de mise en œuvre</t>
   </si>
   <si>
     <t>If the end of the period is missing, it means that the period is ongoing</t>
